--- a/data/trans_orig/P29A_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P29A_R-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consumió bebidas alcohólicas en las últimas dos semanas en 2007</t>
+          <t>Población que consumió bebidas alcohólicas en las últimas dos semanas en 2007 (tasa de respuesta: 99,08%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>411794</t>
+          <t>412864</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>476041</t>
+          <t>474694</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>128746</t>
+          <t>125912</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>171547</t>
+          <t>170506</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>548342</t>
+          <t>550575</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>634921</t>
+          <t>636498</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,28%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>545296</t>
+          <t>546643</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>609543</t>
+          <t>608473</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>59,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1140422</t>
+          <t>1141463</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1183223</t>
+          <t>1186057</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1698385</t>
+          <t>1696808</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1784964</t>
+          <t>1782731</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,4%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>960025</t>
+          <t>967358</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1042307</t>
+          <t>1044398</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>57,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>458109</t>
+          <t>456114</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>531242</t>
+          <t>531836</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1441522</t>
+          <t>1439343</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1550267</t>
+          <t>1556699</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>48,02%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>626241</t>
+          <t>624150</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>708523</t>
+          <t>701190</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>42,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1041687</t>
+          <t>1041093</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1114820</t>
+          <t>1116815</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>66,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1691209</t>
+          <t>1684777</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1799954</t>
+          <t>1802133</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>55,6%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>305051</t>
+          <t>303205</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>350391</t>
+          <t>351643</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>162024</t>
+          <t>158605</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>203086</t>
+          <t>201053</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>480685</t>
+          <t>477649</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>542948</t>
+          <t>545431</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>46,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>53,57%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>192328</t>
+          <t>191076</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>237668</t>
+          <t>239514</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>272295</t>
+          <t>274328</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>313357</t>
+          <t>316776</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>65,92%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>475152</t>
+          <t>472669</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>537415</t>
+          <t>540451</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,79%</t>
+          <t>53,08%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1721081</t>
+          <t>1711533</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1830050</t>
+          <t>1832417</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>56,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>774438</t>
+          <t>776264</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>871859</t>
+          <t>875351</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2521204</t>
+          <t>2521776</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2681089</t>
+          <t>2683702</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>40,71%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1402553</t>
+          <t>1400186</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1511522</t>
+          <t>1521070</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2488420</t>
+          <t>2484928</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2585841</t>
+          <t>2584015</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3911793</t>
+          <t>3909180</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4071678</t>
+          <t>4071106</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>59,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>61,75%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consumió bebidas alcohólicas en las últimas dos semanas en 2012</t>
+          <t>Población que consumió bebidas alcohólicas en las últimas dos semanas en 2012 (tasa de respuesta: 96,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>422655</t>
+          <t>424939</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>486482</t>
+          <t>487081</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>164978</t>
+          <t>164914</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>218234</t>
+          <t>219251</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>599524</t>
+          <t>602236</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>689141</t>
+          <t>690807</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,75%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>443570</t>
+          <t>442971</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>507397</t>
+          <t>505113</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>54,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1097938</t>
+          <t>1096921</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1151194</t>
+          <t>1151258</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1557083</t>
+          <t>1555417</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1646700</t>
+          <t>1643988</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>69,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>73,19%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1027758</t>
+          <t>1024673</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1116154</t>
+          <t>1113933</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>54,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>463691</t>
+          <t>462984</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>543681</t>
+          <t>545080</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1519529</t>
+          <t>1515101</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1637613</t>
+          <t>1639152</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>45,61%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>755842</t>
+          <t>758063</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>844238</t>
+          <t>847323</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>45,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1178377</t>
+          <t>1176978</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1258367</t>
+          <t>1259074</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,43%</t>
+          <t>68,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,07%</t>
+          <t>73,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1956441</t>
+          <t>1954902</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2074525</t>
+          <t>2078953</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>57,84%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>283543</t>
+          <t>281387</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>326519</t>
+          <t>327353</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>70,14%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>180089</t>
+          <t>179106</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>225443</t>
+          <t>225537</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>473411</t>
+          <t>474439</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>536539</t>
+          <t>535337</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>58,87%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>139011</t>
+          <t>138177</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>181987</t>
+          <t>184143</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>218389</t>
+          <t>218295</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>263743</t>
+          <t>264726</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>372824</t>
+          <t>374026</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>435952</t>
+          <t>434924</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>47,83%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1769988</t>
+          <t>1775398</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1888008</t>
+          <t>1892129</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>54,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>57,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>840574</t>
+          <t>841136</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>947231</t>
+          <t>950343</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2642961</t>
+          <t>2646168</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2815066</t>
+          <t>2817569</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,74%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1379570</t>
+          <t>1375449</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1497590</t>
+          <t>1492180</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2534831</t>
+          <t>2531719</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2641488</t>
+          <t>2640926</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3934575</t>
+          <t>3932072</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4106680</t>
+          <t>4103473</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>60,8%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consumió bebidas alcohólicas en las últimas dos semanas en 2016</t>
+          <t>Población que consumió bebidas alcohólicas en las últimas dos semanas en 2016 (tasa de respuesta: 97,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>302283</t>
+          <t>306486</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>357103</t>
+          <t>357766</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>105202</t>
+          <t>104994</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>148709</t>
+          <t>146699</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>420241</t>
+          <t>421060</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>493193</t>
+          <t>495240</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,88%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>374080</t>
+          <t>373417</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>428900</t>
+          <t>424697</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>51,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>58,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>834912</t>
+          <t>836922</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>878419</t>
+          <t>878627</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1221612</t>
+          <t>1219565</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1294564</t>
+          <t>1293745</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,24%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>75,45%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1133928</t>
+          <t>1132134</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1225426</t>
+          <t>1227833</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>56,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>60,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>637267</t>
+          <t>640116</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>719490</t>
+          <t>723761</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1797507</t>
+          <t>1796115</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1926781</t>
+          <t>1928551</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>48,52%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>787752</t>
+          <t>785345</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>879250</t>
+          <t>881044</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1242494</t>
+          <t>1238223</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1324717</t>
+          <t>1321868</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>67,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2048381</t>
+          <t>2046611</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2177655</t>
+          <t>2179047</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>51,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>54,82%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>333390</t>
+          <t>332804</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>377565</t>
+          <t>376695</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>71,72%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>239315</t>
+          <t>240781</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>286583</t>
+          <t>287151</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>45,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>587274</t>
+          <t>587183</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>652628</t>
+          <t>650324</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>55,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>61,56%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>148887</t>
+          <t>149757</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>193062</t>
+          <t>193648</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>243434</t>
+          <t>242866</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>290702</t>
+          <t>289236</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>54,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>403842</t>
+          <t>406146</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>469196</t>
+          <t>469287</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,42%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1816376</t>
+          <t>1808004</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1923115</t>
+          <t>1921889</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>58,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1016756</t>
+          <t>1012874</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1124449</t>
+          <t>1122647</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2862262</t>
+          <t>2858349</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3023349</t>
+          <t>3023574</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>44,82%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1347698</t>
+          <t>1348924</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1454437</t>
+          <t>1462809</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2351173</t>
+          <t>2352975</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2458866</t>
+          <t>2462748</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3723087</t>
+          <t>3722862</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3884174</t>
+          <t>3888087</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,19%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>57,63%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consumió bebidas alcohólicas en las últimas dos semanas en 2023</t>
+          <t>Población que consumió bebidas alcohólicas en las últimas dos semanas en 2023 (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>221321</t>
+          <t>223297</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>263542</t>
+          <t>266681</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>52,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>56863</t>
+          <t>55850</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>83174</t>
+          <t>82445</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>284887</t>
+          <t>285781</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>337874</t>
+          <t>339622</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,87%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>249197</t>
+          <t>246058</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>291418</t>
+          <t>289442</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>668159</t>
+          <t>668888</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>694470</t>
+          <t>695483</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>926198</t>
+          <t>924450</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>979185</t>
+          <t>978291</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>77,39%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>699603</t>
+          <t>728636</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1124623</t>
+          <t>1122017</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>538576</t>
+          <t>539320</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1147301</t>
+          <t>1113278</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1448818</t>
+          <t>1435054</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2079391</t>
+          <t>2059725</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>45,57%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1161300</t>
+          <t>1163906</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1586320</t>
+          <t>1557287</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>50,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1087042</t>
+          <t>1121065</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1695767</t>
+          <t>1695023</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>75,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2440875</t>
+          <t>2460541</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3071448</t>
+          <t>3085212</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>68,25%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>318231</t>
+          <t>319084</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>372953</t>
+          <t>370650</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>49,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,68%</t>
+          <t>57,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>224711</t>
+          <t>225320</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>267566</t>
+          <t>269845</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>554796</t>
+          <t>555227</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>626819</t>
+          <t>629010</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>48,2%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>273670</t>
+          <t>275973</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>328392</t>
+          <t>327539</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>50,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>390742</t>
+          <t>388463</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>433597</t>
+          <t>432988</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>678112</t>
+          <t>675921</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>750135</t>
+          <t>749704</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>57,45%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1248334</t>
+          <t>1198957</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1712669</t>
+          <t>1717427</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>49,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>847834</t>
+          <t>847639</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1513290</t>
+          <t>1585459</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2357641</t>
+          <t>2343538</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3020393</t>
+          <t>3027093</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>42,7%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1732616</t>
+          <t>1727858</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2196951</t>
+          <t>2246328</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>63,77%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2130694</t>
+          <t>2058525</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2796150</t>
+          <t>2796345</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>56,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4068876</t>
+          <t>4062176</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4731628</t>
+          <t>4745731</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>57,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>66,94%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P29A_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P29A_R-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>412864</t>
+          <t>414737</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>474694</t>
+          <t>475387</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>125912</t>
+          <t>125949</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>170506</t>
+          <t>172206</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>550575</t>
+          <t>544962</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>636498</t>
+          <t>632514</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,11%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>546643</t>
+          <t>545950</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>608473</t>
+          <t>606600</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1141463</t>
+          <t>1139763</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1186057</t>
+          <t>1186020</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1696808</t>
+          <t>1700792</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1782731</t>
+          <t>1788344</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>76,64%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>967358</t>
+          <t>957699</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1044398</t>
+          <t>1038337</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>62,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>456114</t>
+          <t>456932</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>531836</t>
+          <t>528898</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1439343</t>
+          <t>1442771</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1556699</t>
+          <t>1558692</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>48,09%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>624150</t>
+          <t>630211</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>701190</t>
+          <t>710849</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1041093</t>
+          <t>1044031</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1116815</t>
+          <t>1115997</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1684777</t>
+          <t>1682784</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1802133</t>
+          <t>1798705</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>51,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>55,49%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>303205</t>
+          <t>302759</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>351643</t>
+          <t>350263</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>55,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>64,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>158605</t>
+          <t>163822</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>201053</t>
+          <t>206206</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>477649</t>
+          <t>479497</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>545431</t>
+          <t>545320</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>53,56%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>191076</t>
+          <t>192456</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>239514</t>
+          <t>239960</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>44,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>274328</t>
+          <t>269175</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>316776</t>
+          <t>311559</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>56,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>472669</t>
+          <t>472780</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>540451</t>
+          <t>538603</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>52,9%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1711533</t>
+          <t>1720474</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1832417</t>
+          <t>1832180</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>53,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>776264</t>
+          <t>771836</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>875351</t>
+          <t>872284</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2521776</t>
+          <t>2512024</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2683702</t>
+          <t>2675544</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>40,58%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1400186</t>
+          <t>1400423</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1521070</t>
+          <t>1512129</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2484928</t>
+          <t>2487995</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2584015</t>
+          <t>2588443</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3909180</t>
+          <t>3917338</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4071106</t>
+          <t>4080858</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>61,9%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>424939</t>
+          <t>425762</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>487081</t>
+          <t>486256</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>52,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>164914</t>
+          <t>164283</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>219251</t>
+          <t>216216</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>602236</t>
+          <t>599176</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>690807</t>
+          <t>692799</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,84%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>442971</t>
+          <t>443796</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>505113</t>
+          <t>504290</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>47,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1096921</t>
+          <t>1099956</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1151258</t>
+          <t>1151889</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1555417</t>
+          <t>1553425</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1643988</t>
+          <t>1647048</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,25%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>73,33%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1024673</t>
+          <t>1031920</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1113933</t>
+          <t>1116684</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>55,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>462984</t>
+          <t>460936</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>545080</t>
+          <t>538623</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1515101</t>
+          <t>1515592</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1639152</t>
+          <t>1636647</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>45,54%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>758063</t>
+          <t>755312</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>847323</t>
+          <t>840076</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1176978</t>
+          <t>1183435</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1259074</t>
+          <t>1261122</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,35%</t>
+          <t>68,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>73,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1954902</t>
+          <t>1957407</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2078953</t>
+          <t>2078462</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54,39%</t>
+          <t>54,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>57,83%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>281387</t>
+          <t>282967</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>327353</t>
+          <t>328376</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>60,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>179106</t>
+          <t>177810</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>225537</t>
+          <t>223335</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,82%</t>
+          <t>50,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>474439</t>
+          <t>472332</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>535337</t>
+          <t>539329</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>59,31%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>138177</t>
+          <t>137154</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>184143</t>
+          <t>182563</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>218295</t>
+          <t>220497</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>264726</t>
+          <t>266022</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>49,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>59,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>374026</t>
+          <t>370034</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>434924</t>
+          <t>437031</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>48,06%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1775398</t>
+          <t>1776735</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1892129</t>
+          <t>1886734</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>841136</t>
+          <t>847561</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>950343</t>
+          <t>947203</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2646168</t>
+          <t>2646670</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2817569</t>
+          <t>2813156</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>41,68%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1375449</t>
+          <t>1380844</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1492180</t>
+          <t>1490843</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2531719</t>
+          <t>2534859</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2640926</t>
+          <t>2634501</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>75,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3932072</t>
+          <t>3936485</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4103473</t>
+          <t>4102971</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>60,79%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>306486</t>
+          <t>306552</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>357766</t>
+          <t>360553</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>49,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>104994</t>
+          <t>104982</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>146699</t>
+          <t>147167</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>421060</t>
+          <t>422011</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>495240</t>
+          <t>495385</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>28,89%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>373417</t>
+          <t>370630</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>424697</t>
+          <t>424631</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>50,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>58,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>836922</t>
+          <t>836454</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>878627</t>
+          <t>878639</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1219565</t>
+          <t>1219420</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1293745</t>
+          <t>1292794</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>75,39%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1132134</t>
+          <t>1132981</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1227833</t>
+          <t>1225005</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>640116</t>
+          <t>641713</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>723761</t>
+          <t>724630</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1796115</t>
+          <t>1797255</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1928551</t>
+          <t>1926287</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>48,46%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>785345</t>
+          <t>788173</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>881044</t>
+          <t>880197</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1238223</t>
+          <t>1237354</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1321868</t>
+          <t>1320271</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>63,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>67,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2046611</t>
+          <t>2048875</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2179047</t>
+          <t>2177907</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>54,79%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>332804</t>
+          <t>331621</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>376695</t>
+          <t>374905</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>62,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>240781</t>
+          <t>242728</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>287151</t>
+          <t>287260</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,18%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>587183</t>
+          <t>587435</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>650324</t>
+          <t>652261</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,58%</t>
+          <t>55,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>61,74%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>149757</t>
+          <t>151547</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>193648</t>
+          <t>194831</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>242866</t>
+          <t>242757</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>289236</t>
+          <t>287289</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>406146</t>
+          <t>404209</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>469287</t>
+          <t>469035</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>44,4%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1808004</t>
+          <t>1812574</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1921889</t>
+          <t>1925510</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>55,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>58,76%</t>
+          <t>58,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1012874</t>
+          <t>1017917</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1122647</t>
+          <t>1121170</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2858349</t>
+          <t>2861088</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3023574</t>
+          <t>3019203</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>44,75%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1348924</t>
+          <t>1345303</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1462809</t>
+          <t>1458239</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2352975</t>
+          <t>2354452</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2462748</t>
+          <t>2457705</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>67,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3722862</t>
+          <t>3727233</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3888087</t>
+          <t>3885348</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>55,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>57,59%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>243958</t>
+          <t>258511</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>223297</t>
+          <t>235067</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>266681</t>
+          <t>282618</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>40,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>49,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>67333</t>
+          <t>74933</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>55850</t>
+          <t>62712</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>82445</t>
+          <t>88715</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>311290</t>
+          <t>333444</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>285781</t>
+          <t>308072</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>339622</t>
+          <t>364234</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,1%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>268781</t>
+          <t>317737</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>246058</t>
+          <t>293630</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>289442</t>
+          <t>341181</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>55,14%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>50,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>59,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>684000</t>
+          <t>744356</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>668888</t>
+          <t>730574</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>695483</t>
+          <t>756577</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>952782</t>
+          <t>1062093</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>924450</t>
+          <t>1031303</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>978291</t>
+          <t>1087465</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>75,37%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>77,92%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>512739</t>
+          <t>576248</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>512739</t>
+          <t>576248</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>512739</t>
+          <t>576248</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>751333</t>
+          <t>819289</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>751333</t>
+          <t>819289</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>751333</t>
+          <t>819289</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1264072</t>
+          <t>1395537</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1264072</t>
+          <t>1395537</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1264072</t>
+          <t>1395537</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>985825</t>
+          <t>1047639</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>728636</t>
+          <t>994589</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1122017</t>
+          <t>1101580</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>709850</t>
+          <t>560023</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>539320</t>
+          <t>522430</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1113278</t>
+          <t>596926</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1695675</t>
+          <t>1607662</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1435054</t>
+          <t>1539178</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2059725</t>
+          <t>1682491</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>38,3%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1300098</t>
+          <t>1178410</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1163906</t>
+          <t>1124469</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1557287</t>
+          <t>1231460</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>56,87%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>50,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>55,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1524493</t>
+          <t>1607061</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1121065</t>
+          <t>1570158</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1695023</t>
+          <t>1644654</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>75,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2824591</t>
+          <t>2785471</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2460541</t>
+          <t>2710642</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3085212</t>
+          <t>2853955</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>61,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>64,96%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2285923</t>
+          <t>2226049</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2285923</t>
+          <t>2226049</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2285923</t>
+          <t>2226049</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2234343</t>
+          <t>2167084</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2234343</t>
+          <t>2167084</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2234343</t>
+          <t>2167084</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4520266</t>
+          <t>4393133</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4520266</t>
+          <t>4393133</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4520266</t>
+          <t>4393133</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>344253</t>
+          <t>368029</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>319084</t>
+          <t>339703</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>370650</t>
+          <t>399170</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>47,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>56,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>246303</t>
+          <t>270040</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>225320</t>
+          <t>247700</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>269845</t>
+          <t>296070</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>590556</t>
+          <t>638069</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>555227</t>
+          <t>600470</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>629010</t>
+          <t>673125</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>46,61%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>302370</t>
+          <t>343558</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>275973</t>
+          <t>312417</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>327539</t>
+          <t>371884</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>43,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>412005</t>
+          <t>462397</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>388463</t>
+          <t>436367</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>432988</t>
+          <t>484737</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>59,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>714375</t>
+          <t>805955</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>675921</t>
+          <t>770899</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>749704</t>
+          <t>843554</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>55,81%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>53,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>58,42%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>658308</t>
+          <t>732437</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>658308</t>
+          <t>732437</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>658308</t>
+          <t>732437</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1304931</t>
+          <t>1444024</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1304931</t>
+          <t>1444024</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1304931</t>
+          <t>1444024</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1574035</t>
+          <t>1674178</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1198957</t>
+          <t>1605796</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1717427</t>
+          <t>1744327</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>45,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>49,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1023486</t>
+          <t>904997</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>847639</t>
+          <t>858469</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1585459</t>
+          <t>954603</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2597521</t>
+          <t>2579176</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2343538</t>
+          <t>2503982</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3027093</t>
+          <t>2671552</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>36,94%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1871250</t>
+          <t>1839706</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1727858</t>
+          <t>1769557</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2246328</t>
+          <t>1908088</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>54,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2620498</t>
+          <t>2813813</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2058525</t>
+          <t>2764207</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2796345</t>
+          <t>2860341</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>75,66%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>4491748</t>
+          <t>4653518</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4062176</t>
+          <t>4561142</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4745731</t>
+          <t>4728712</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,94%</t>
+          <t>65,38%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3445285</t>
+          <t>3513884</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3445285</t>
+          <t>3513884</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3445285</t>
+          <t>3513884</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3643984</t>
+          <t>3718810</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3643984</t>
+          <t>3718810</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3643984</t>
+          <t>3718810</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7089269</t>
+          <t>7232694</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7089269</t>
+          <t>7232694</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7089269</t>
+          <t>7232694</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
